--- a/UAE_Retail_Analytics_Project_Starter.xlsx
+++ b/UAE_Retail_Analytics_Project_Starter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Documents\UAE-Retail-Operations-Analytics\Clone\uae-retail-operations-analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0ABAB15-3C1A-4C67-AC28-21FA0EE9152A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE19B29A-426C-4C08-A594-26274E2087F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3047" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3046" uniqueCount="525">
   <si>
     <t>Order_ID</t>
   </si>
@@ -1549,9 +1549,6 @@
   </si>
   <si>
     <t>Channel_Sales</t>
-  </si>
-  <si>
-    <t>Category_Clean</t>
   </si>
   <si>
     <t>UAE Retail Operations Analytics</t>
@@ -1772,7 +1769,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1820,34 +1817,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1880,22 +1853,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1915,15 +1877,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1956,6 +1913,18 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1968,30 +1937,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="20">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2001,27 +1957,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
@@ -2477,6 +2412,14 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.35162207938579498"/>
+          <c:y val="2.361471202757405E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2978,10 +2921,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.19196168464760638"/>
-          <c:y val="0.26069225721784778"/>
-          <c:w val="0.74303827484574081"/>
-          <c:h val="0.52549613589967925"/>
+          <c:x val="0.1601180469103578"/>
+          <c:y val="0.1229396783564656"/>
+          <c:w val="0.77488190642472787"/>
+          <c:h val="0.66324862820836239"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -3228,6 +3171,14 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="4.6429082354658632E-2"/>
+              <c:y val="0.39236866718193431"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -3338,6 +3289,14 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.50824986930341531"/>
+              <c:y val="0.89717063519856499"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -6425,10 +6384,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="9.7138888888888886E-2"/>
-          <c:y val="0.23393518518518519"/>
-          <c:w val="0.86952777777777779"/>
-          <c:h val="0.53054972295129788"/>
+          <c:x val="8.4734070029997541E-2"/>
+          <c:y val="0.10991988282030227"/>
+          <c:w val="0.88193262454395982"/>
+          <c:h val="0.70341936867958321"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -8950,10 +8909,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.15670468776404836"/>
-          <c:y val="0.2021212929364602"/>
-          <c:w val="0.3258784211911987"/>
-          <c:h val="0.69655929020962704"/>
+          <c:x val="0.1602489665232511"/>
+          <c:y val="0.18834103003241789"/>
+          <c:w val="0.35423226624225257"/>
+          <c:h val="0.74652766341860477"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -9168,7 +9127,7 @@
           <c:yMode val="edge"/>
           <c:x val="0.67219743626187556"/>
           <c:y val="0.27155189245690198"/>
-          <c:w val="0.11282873495169209"/>
+          <c:w val="0.17145293473535317"/>
           <c:h val="0.62424514682649113"/>
         </c:manualLayout>
       </c:layout>
@@ -10965,14 +10924,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>3161</xdr:rowOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>173791</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
+      <xdr:rowOff>31751</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -20369,27 +20328,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AA4D7DCE-1538-41A1-A2C0-6578A8D32256}" name="Table1" displayName="Table1" ref="A1:P421" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
-  <autoFilter ref="A1:P421" xr:uid="{AA4D7DCE-1538-41A1-A2C0-6578A8D32256}"/>
-  <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{E706A746-E39E-428F-9A55-73DDA1075645}" name="Order_ID" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{890F097F-809C-4554-9DC4-D263D45C8FC8}" name="Order_Date" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{A358C24B-A50E-4B20-BDCD-C70DC38D69E4}" name="Region" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{F02E4044-D3F2-496F-A406-FE71D644AE87}" name="Sales_Channel" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{73D1FEB2-8801-458D-956E-A74F902EE905}" name="Product_Category" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{1879CAAF-5E01-4FE4-9057-9F042A64B043}" name="Product" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{993282AB-D0FE-47F5-AE37-0C130C7BFB06}" name="Units_Sold" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{C400AE41-B594-4AF6-9846-158BC6F46524}" name="Unit_Price_AED" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{A297BC57-6E2B-49AB-9925-BC3869B94D1C}" name="Discount_Pct" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{3EBBA28B-232E-4B3C-99A0-8EA7B10463B0}" name="Sales_AED" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{D1EC8DF2-9F7B-4FAA-95FF-5BB2A746DC3C}" name="Cost_AED" dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{EC93E946-649A-4108-926B-634E288C6D5A}" name="Order_Status" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{DD4294B5-FCF2-4B72-B980-8A5536EE2319}" name="Delivery_Days" dataDxfId="4"/>
-    <tableColumn id="14" xr3:uid="{C10B4EEE-17F1-4D81-8DCD-EE310F08592A}" name="Customer_Rating" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{F3A768B9-58F2-4823-9F63-CBCFC3DBB24E}" name="Returned" dataDxfId="2"/>
-    <tableColumn id="18" xr3:uid="{00D5491F-CA12-49E0-9890-8819CF393F0F}" name="Category_Clean" dataDxfId="1">
-      <calculatedColumnFormula>PROPER(TRIM(E2))</calculatedColumnFormula>
-    </tableColumn>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AA4D7DCE-1538-41A1-A2C0-6578A8D32256}" name="Table1" displayName="Table1" ref="A1:O421" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
+  <autoFilter ref="A1:O421" xr:uid="{AA4D7DCE-1538-41A1-A2C0-6578A8D32256}"/>
+  <tableColumns count="15">
+    <tableColumn id="1" xr3:uid="{E706A746-E39E-428F-9A55-73DDA1075645}" name="Order_ID" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{890F097F-809C-4554-9DC4-D263D45C8FC8}" name="Order_Date" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{A358C24B-A50E-4B20-BDCD-C70DC38D69E4}" name="Region" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{F02E4044-D3F2-496F-A406-FE71D644AE87}" name="Sales_Channel" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{73D1FEB2-8801-458D-956E-A74F902EE905}" name="Product_Category" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{1879CAAF-5E01-4FE4-9057-9F042A64B043}" name="Product" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{993282AB-D0FE-47F5-AE37-0C130C7BFB06}" name="Units_Sold" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{C400AE41-B594-4AF6-9846-158BC6F46524}" name="Unit_Price_AED" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{A297BC57-6E2B-49AB-9925-BC3869B94D1C}" name="Discount_Pct" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{3EBBA28B-232E-4B3C-99A0-8EA7B10463B0}" name="Sales_AED" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{D1EC8DF2-9F7B-4FAA-95FF-5BB2A746DC3C}" name="Cost_AED" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{EC93E946-649A-4108-926B-634E288C6D5A}" name="Order_Status" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{DD4294B5-FCF2-4B72-B980-8A5536EE2319}" name="Delivery_Days" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{C10B4EEE-17F1-4D81-8DCD-EE310F08592A}" name="Customer_Rating" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{F3A768B9-58F2-4823-9F63-CBCFC3DBB24E}" name="Returned" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -20688,10 +20644,10 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="25" t="s">
         <v>496</v>
       </c>
-      <c r="B4" s="34"/>
+      <c r="B4" s="26"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
@@ -20767,10 +20723,10 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="27" t="s">
         <v>499</v>
       </c>
-      <c r="B4" s="36"/>
+      <c r="B4" s="28"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
@@ -20784,7 +20740,7 @@
       <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="38">
+      <c r="B6">
         <v>72649.569999999992</v>
       </c>
     </row>
@@ -20792,7 +20748,7 @@
       <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="38">
+      <c r="B7">
         <v>32590.409999999996</v>
       </c>
     </row>
@@ -20800,7 +20756,7 @@
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="38">
+      <c r="B8">
         <v>28956.720000000005</v>
       </c>
     </row>
@@ -20808,7 +20764,7 @@
       <c r="A9" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="B9" s="38">
+      <c r="B9">
         <v>134196.69999999998</v>
       </c>
     </row>
@@ -20830,10 +20786,10 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="27" t="s">
         <v>498</v>
       </c>
-      <c r="B4" s="36"/>
+      <c r="B4" s="28"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
@@ -20910,22 +20866,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="31" t="s">
         <v>501</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-    </row>
-    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
-        <v>502</v>
-      </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="33"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
@@ -20933,27 +20889,27 @@
       <c r="E3" s="7"/>
     </row>
     <row r="4" spans="1:5" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="13" t="s">
+        <v>502</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>503</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="E4" s="13" t="s">
         <v>504</v>
       </c>
-      <c r="E4" s="16" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
-        <v>506</v>
-      </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="19">
+      <c r="B5" s="15"/>
+      <c r="C5" s="16">
         <f>COUNTA('[1]Raw Data'!A2:A421)</f>
         <v>420</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19">
+      <c r="D5" s="15"/>
+      <c r="E5" s="16">
         <f>SUM(Raw_Data!G2:G421)</f>
         <v>1236</v>
       </c>
@@ -20970,7 +20926,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P421"/>
+  <dimension ref="A1:O421"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.88671875" customWidth="1"/>
@@ -20988,10 +20944,10 @@
     <col min="13" max="13" width="15" customWidth="1"/>
     <col min="14" max="14" width="23.5546875" customWidth="1"/>
     <col min="15" max="15" width="17.44140625" customWidth="1"/>
-    <col min="16" max="16" width="23.6640625" customWidth="1"/>
+    <col min="16" max="16" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -21037,11 +20993,8 @@
       <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="15" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>77</v>
       </c>
@@ -21087,12 +21040,8 @@
       <c r="O2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P2" s="10" t="str">
-        <f t="shared" ref="P2:P65" si="0">PROPER(TRIM(E2))</f>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>377</v>
       </c>
@@ -21138,12 +21087,8 @@
       <c r="O3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P3" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>321</v>
       </c>
@@ -21189,12 +21134,8 @@
       <c r="O4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P4" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>231</v>
       </c>
@@ -21236,12 +21177,8 @@
       <c r="O5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P5" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>223</v>
       </c>
@@ -21287,12 +21224,8 @@
       <c r="O6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P6" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>418</v>
       </c>
@@ -21338,12 +21271,8 @@
       <c r="O7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P7" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>75</v>
       </c>
@@ -21385,12 +21314,8 @@
       <c r="O8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P8" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>341</v>
       </c>
@@ -21436,12 +21361,8 @@
       <c r="O9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P9" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>138</v>
       </c>
@@ -21487,12 +21408,8 @@
       <c r="O10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P10" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>84</v>
       </c>
@@ -21538,12 +21455,8 @@
       <c r="O11" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P11" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>277</v>
       </c>
@@ -21585,12 +21498,8 @@
       <c r="O12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P12" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>460</v>
       </c>
@@ -21636,12 +21545,8 @@
       <c r="O13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P13" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>358</v>
       </c>
@@ -21687,12 +21592,8 @@
       <c r="O14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P14" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>370</v>
       </c>
@@ -21738,12 +21639,8 @@
       <c r="O15" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P15" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>350</v>
       </c>
@@ -21789,12 +21686,8 @@
       <c r="O16" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P16" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>385</v>
       </c>
@@ -21840,12 +21733,8 @@
       <c r="O17" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>273</v>
       </c>
@@ -21887,12 +21776,8 @@
       <c r="O18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P18" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>99</v>
       </c>
@@ -21938,12 +21823,8 @@
       <c r="O19" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P19" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>409</v>
       </c>
@@ -21989,12 +21870,8 @@
       <c r="O20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P20" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>239</v>
       </c>
@@ -22040,12 +21917,8 @@
       <c r="O21" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P21" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>269</v>
       </c>
@@ -22091,12 +21964,8 @@
       <c r="O22" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P22" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>206</v>
       </c>
@@ -22138,12 +22007,8 @@
       <c r="O23" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P23" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>130</v>
       </c>
@@ -22189,12 +22054,8 @@
       <c r="O24" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P24" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>438</v>
       </c>
@@ -22236,12 +22097,8 @@
       <c r="O25" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P25" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>383</v>
       </c>
@@ -22283,12 +22140,8 @@
       <c r="O26" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P26" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>318</v>
       </c>
@@ -22330,12 +22183,8 @@
       <c r="O27" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P27" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>213</v>
       </c>
@@ -22381,12 +22230,8 @@
       <c r="O28" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P28" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>401</v>
       </c>
@@ -22428,12 +22273,8 @@
       <c r="O29" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P29" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>284</v>
       </c>
@@ -22479,12 +22320,8 @@
       <c r="O30" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P30" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>234</v>
       </c>
@@ -22526,12 +22363,8 @@
       <c r="O31" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P31" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>241</v>
       </c>
@@ -22577,12 +22410,8 @@
       <c r="O32" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P32" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>141</v>
       </c>
@@ -22624,12 +22453,8 @@
       <c r="O33" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P33" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>79</v>
       </c>
@@ -22671,12 +22496,8 @@
       <c r="O34" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P34" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>286</v>
       </c>
@@ -22722,12 +22543,8 @@
       <c r="O35" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P35" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>421</v>
       </c>
@@ -22769,12 +22586,8 @@
       <c r="O36" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P36" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
         <v>64</v>
       </c>
@@ -22820,12 +22633,8 @@
       <c r="O37" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P37" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>417</v>
       </c>
@@ -22871,12 +22680,8 @@
       <c r="O38" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P38" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
         <v>404</v>
       </c>
@@ -22922,12 +22727,8 @@
       <c r="O39" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P39" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
         <v>163</v>
       </c>
@@ -22973,12 +22774,8 @@
       <c r="O40" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P40" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
         <v>313</v>
       </c>
@@ -23020,12 +22817,8 @@
       <c r="O41" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P41" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
         <v>120</v>
       </c>
@@ -23071,12 +22864,8 @@
       <c r="O42" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P42" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
         <v>366</v>
       </c>
@@ -23122,12 +22911,8 @@
       <c r="O43" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P43" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>346</v>
       </c>
@@ -23173,12 +22958,8 @@
       <c r="O44" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P44" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
         <v>199</v>
       </c>
@@ -23220,12 +23001,8 @@
       <c r="O45" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P45" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>65</v>
       </c>
@@ -23267,12 +23044,8 @@
       <c r="O46" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P46" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
         <v>458</v>
       </c>
@@ -23314,12 +23087,8 @@
       <c r="O47" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P47" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>235</v>
       </c>
@@ -23365,12 +23134,8 @@
       <c r="O48" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P48" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
         <v>423</v>
       </c>
@@ -23416,12 +23181,8 @@
       <c r="O49" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P49" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>334</v>
       </c>
@@ -23467,12 +23228,8 @@
       <c r="O50" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P50" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="9" t="s">
         <v>380</v>
       </c>
@@ -23514,12 +23271,8 @@
       <c r="O51" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P51" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>369</v>
       </c>
@@ -23565,12 +23318,8 @@
       <c r="O52" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P52" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="9" t="s">
         <v>133</v>
       </c>
@@ -23616,12 +23365,8 @@
       <c r="O53" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P53" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>200</v>
       </c>
@@ -23667,12 +23412,8 @@
       <c r="O54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P54" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
         <v>250</v>
       </c>
@@ -23714,12 +23455,8 @@
       <c r="O55" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P55" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
         <v>264</v>
       </c>
@@ -23765,12 +23502,8 @@
       <c r="O56" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P56" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
         <v>54</v>
       </c>
@@ -23816,12 +23549,8 @@
       <c r="O57" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P57" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
         <v>283</v>
       </c>
@@ -23867,12 +23596,8 @@
       <c r="O58" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P58" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
         <v>115</v>
       </c>
@@ -23918,12 +23643,8 @@
       <c r="O59" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P59" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
         <v>362</v>
       </c>
@@ -23969,12 +23690,8 @@
       <c r="O60" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P60" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
         <v>338</v>
       </c>
@@ -24020,12 +23737,8 @@
       <c r="O61" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P61" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
         <v>436</v>
       </c>
@@ -24071,12 +23784,8 @@
       <c r="O62" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P62" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
         <v>361</v>
       </c>
@@ -24118,12 +23827,8 @@
       <c r="O63" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P63" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
         <v>203</v>
       </c>
@@ -24169,12 +23874,8 @@
       <c r="O64" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P64" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
         <v>454</v>
       </c>
@@ -24220,12 +23921,8 @@
       <c r="O65" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P65" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
         <v>216</v>
       </c>
@@ -24271,12 +23968,8 @@
       <c r="O66" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P66" s="10" t="str">
-        <f t="shared" ref="P66:P129" si="1">PROPER(TRIM(E66))</f>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
         <v>189</v>
       </c>
@@ -24322,12 +24015,8 @@
       <c r="O67" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P67" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
         <v>431</v>
       </c>
@@ -24369,12 +24058,8 @@
       <c r="O68" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P68" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
         <v>208</v>
       </c>
@@ -24416,12 +24101,8 @@
       <c r="O69" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P69" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
         <v>67</v>
       </c>
@@ -24467,12 +24148,8 @@
       <c r="O70" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P70" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
         <v>252</v>
       </c>
@@ -24514,12 +24191,8 @@
       <c r="O71" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P71" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
         <v>391</v>
       </c>
@@ -24565,12 +24238,8 @@
       <c r="O72" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P72" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
         <v>132</v>
       </c>
@@ -24616,12 +24285,8 @@
       <c r="O73" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P73" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="9" t="s">
         <v>247</v>
       </c>
@@ -24667,12 +24332,8 @@
       <c r="O74" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P74" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="9" t="s">
         <v>102</v>
       </c>
@@ -24718,12 +24379,8 @@
       <c r="O75" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P75" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
         <v>340</v>
       </c>
@@ -24769,12 +24426,8 @@
       <c r="O76" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P76" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
         <v>256</v>
       </c>
@@ -24816,12 +24469,8 @@
       <c r="O77" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P77" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
         <v>190</v>
       </c>
@@ -24863,12 +24512,8 @@
       <c r="O78" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P78" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="9" t="s">
         <v>142</v>
       </c>
@@ -24910,12 +24555,8 @@
       <c r="O79" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P79" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="9" t="s">
         <v>294</v>
       </c>
@@ -24961,12 +24602,8 @@
       <c r="O80" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P80" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="9" t="s">
         <v>332</v>
       </c>
@@ -25012,12 +24649,8 @@
       <c r="O81" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P81" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
         <v>445</v>
       </c>
@@ -25063,12 +24696,8 @@
       <c r="O82" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P82" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
         <v>228</v>
       </c>
@@ -25110,12 +24739,8 @@
       <c r="O83" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P83" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
         <v>116</v>
       </c>
@@ -25161,12 +24786,8 @@
       <c r="O84" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P84" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="9" t="s">
         <v>407</v>
       </c>
@@ -25212,12 +24833,8 @@
       <c r="O85" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P85" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="9" t="s">
         <v>312</v>
       </c>
@@ -25263,12 +24880,8 @@
       <c r="O86" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P86" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="9" t="s">
         <v>345</v>
       </c>
@@ -25314,12 +24927,8 @@
       <c r="O87" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P87" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="9" t="s">
         <v>86</v>
       </c>
@@ -25365,12 +24974,8 @@
       <c r="O88" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P88" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="9" t="s">
         <v>182</v>
       </c>
@@ -25416,12 +25021,8 @@
       <c r="O89" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P89" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="9" t="s">
         <v>374</v>
       </c>
@@ -25463,12 +25064,8 @@
       <c r="O90" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P90" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="9" t="s">
         <v>408</v>
       </c>
@@ -25514,12 +25111,8 @@
       <c r="O91" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P91" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="9" t="s">
         <v>224</v>
       </c>
@@ -25565,12 +25158,8 @@
       <c r="O92" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P92" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="9" t="s">
         <v>395</v>
       </c>
@@ -25616,12 +25205,8 @@
       <c r="O93" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P93" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="9" t="s">
         <v>410</v>
       </c>
@@ -25667,12 +25252,8 @@
       <c r="O94" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P94" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="9" t="s">
         <v>212</v>
       </c>
@@ -25718,12 +25299,8 @@
       <c r="O95" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P95" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" s="9" t="s">
         <v>427</v>
       </c>
@@ -25765,12 +25342,8 @@
       <c r="O96" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P96" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="9" t="s">
         <v>168</v>
       </c>
@@ -25812,12 +25385,8 @@
       <c r="O97" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P97" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="9" t="s">
         <v>147</v>
       </c>
@@ -25863,12 +25432,8 @@
       <c r="O98" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P98" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="9" t="s">
         <v>339</v>
       </c>
@@ -25914,12 +25479,8 @@
       <c r="O99" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P99" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
         <v>317</v>
       </c>
@@ -25961,12 +25522,8 @@
       <c r="O100" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P100" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="9" t="s">
         <v>106</v>
       </c>
@@ -26012,12 +25569,8 @@
       <c r="O101" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P101" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="9" t="s">
         <v>405</v>
       </c>
@@ -26063,12 +25616,8 @@
       <c r="O102" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P102" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" s="9" t="s">
         <v>135</v>
       </c>
@@ -26114,12 +25663,8 @@
       <c r="O103" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P103" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="9" t="s">
         <v>394</v>
       </c>
@@ -26165,12 +25710,8 @@
       <c r="O104" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P104" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" s="9" t="s">
         <v>22</v>
       </c>
@@ -26216,12 +25757,8 @@
       <c r="O105" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P105" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="9" t="s">
         <v>392</v>
       </c>
@@ -26267,12 +25804,8 @@
       <c r="O106" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P106" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" s="9" t="s">
         <v>389</v>
       </c>
@@ -26318,12 +25851,8 @@
       <c r="O107" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P107" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" s="9" t="s">
         <v>382</v>
       </c>
@@ -26369,12 +25898,8 @@
       <c r="O108" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P108" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" s="9" t="s">
         <v>326</v>
       </c>
@@ -26420,12 +25945,8 @@
       <c r="O109" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P109" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" s="9" t="s">
         <v>255</v>
       </c>
@@ -26471,12 +25992,8 @@
       <c r="O110" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P110" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" s="9" t="s">
         <v>348</v>
       </c>
@@ -26522,12 +26039,8 @@
       <c r="O111" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P111" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="9" t="s">
         <v>161</v>
       </c>
@@ -26573,12 +26086,8 @@
       <c r="O112" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P112" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" s="9" t="s">
         <v>381</v>
       </c>
@@ -26624,12 +26133,8 @@
       <c r="O113" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P113" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="9" t="s">
         <v>290</v>
       </c>
@@ -26675,12 +26180,8 @@
       <c r="O114" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P114" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" s="9" t="s">
         <v>245</v>
       </c>
@@ -26722,12 +26223,8 @@
       <c r="O115" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P115" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" s="9" t="s">
         <v>272</v>
       </c>
@@ -26773,12 +26270,8 @@
       <c r="O116" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P116" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" s="9" t="s">
         <v>296</v>
       </c>
@@ -26824,12 +26317,8 @@
       <c r="O117" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P117" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" s="9" t="s">
         <v>52</v>
       </c>
@@ -26875,12 +26364,8 @@
       <c r="O118" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P118" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" s="9" t="s">
         <v>108</v>
       </c>
@@ -26926,12 +26411,8 @@
       <c r="O119" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P119" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" s="9" t="s">
         <v>150</v>
       </c>
@@ -26977,12 +26458,8 @@
       <c r="O120" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P120" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" s="9" t="s">
         <v>93</v>
       </c>
@@ -27028,12 +26505,8 @@
       <c r="O121" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P121" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" s="9" t="s">
         <v>230</v>
       </c>
@@ -27079,12 +26552,8 @@
       <c r="O122" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P122" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" s="9" t="s">
         <v>330</v>
       </c>
@@ -27130,12 +26599,8 @@
       <c r="O123" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P123" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" s="9" t="s">
         <v>320</v>
       </c>
@@ -27181,12 +26646,8 @@
       <c r="O124" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P124" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" s="9" t="s">
         <v>251</v>
       </c>
@@ -27232,12 +26693,8 @@
       <c r="O125" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P125" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" s="9" t="s">
         <v>414</v>
       </c>
@@ -27283,12 +26740,8 @@
       <c r="O126" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P126" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" s="9" t="s">
         <v>295</v>
       </c>
@@ -27334,12 +26787,8 @@
       <c r="O127" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P127" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" s="9" t="s">
         <v>70</v>
       </c>
@@ -27385,12 +26834,8 @@
       <c r="O128" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P128" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" s="9" t="s">
         <v>372</v>
       </c>
@@ -27436,12 +26881,8 @@
       <c r="O129" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P129" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" s="9" t="s">
         <v>298</v>
       </c>
@@ -27487,12 +26928,8 @@
       <c r="O130" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P130" s="10" t="str">
-        <f t="shared" ref="P130:P193" si="2">PROPER(TRIM(E130))</f>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" s="9" t="s">
         <v>315</v>
       </c>
@@ -27538,12 +26975,8 @@
       <c r="O131" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P131" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" s="9" t="s">
         <v>293</v>
       </c>
@@ -27589,12 +27022,8 @@
       <c r="O132" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P132" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" s="9" t="s">
         <v>288</v>
       </c>
@@ -27640,12 +27069,8 @@
       <c r="O133" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P133" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" s="9" t="s">
         <v>81</v>
       </c>
@@ -27691,12 +27116,8 @@
       <c r="O134" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P134" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" s="9" t="s">
         <v>292</v>
       </c>
@@ -27742,12 +27163,8 @@
       <c r="O135" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P135" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" s="9" t="s">
         <v>393</v>
       </c>
@@ -27793,12 +27210,8 @@
       <c r="O136" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P136" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" s="9" t="s">
         <v>175</v>
       </c>
@@ -27844,12 +27257,8 @@
       <c r="O137" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P137" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" s="9" t="s">
         <v>305</v>
       </c>
@@ -27891,12 +27300,8 @@
       <c r="O138" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P138" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" s="9" t="s">
         <v>50</v>
       </c>
@@ -27942,12 +27347,8 @@
       <c r="O139" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P139" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140" s="9" t="s">
         <v>198</v>
       </c>
@@ -27993,12 +27394,8 @@
       <c r="O140" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P140" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" s="9" t="s">
         <v>229</v>
       </c>
@@ -28040,12 +27437,8 @@
       <c r="O141" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P141" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" s="9" t="s">
         <v>461</v>
       </c>
@@ -28091,12 +27484,8 @@
       <c r="O142" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P142" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" s="9" t="s">
         <v>139</v>
       </c>
@@ -28138,12 +27527,8 @@
       <c r="O143" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P143" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" s="9" t="s">
         <v>159</v>
       </c>
@@ -28189,12 +27574,8 @@
       <c r="O144" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P144" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145" s="9" t="s">
         <v>218</v>
       </c>
@@ -28240,12 +27621,8 @@
       <c r="O145" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P145" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" s="9" t="s">
         <v>465</v>
       </c>
@@ -28287,12 +27664,8 @@
       <c r="O146" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P146" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147" s="9" t="s">
         <v>413</v>
       </c>
@@ -28338,12 +27711,8 @@
       <c r="O147" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P147" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" s="9" t="s">
         <v>51</v>
       </c>
@@ -28389,12 +27758,8 @@
       <c r="O148" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P148" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A149" s="9" t="s">
         <v>145</v>
       </c>
@@ -28440,12 +27805,8 @@
       <c r="O149" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P149" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150" s="9" t="s">
         <v>400</v>
       </c>
@@ -28491,12 +27852,8 @@
       <c r="O150" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P150" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" s="9" t="s">
         <v>61</v>
       </c>
@@ -28542,12 +27899,8 @@
       <c r="O151" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P151" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" s="9" t="s">
         <v>415</v>
       </c>
@@ -28593,12 +27946,8 @@
       <c r="O152" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P152" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153" s="9" t="s">
         <v>164</v>
       </c>
@@ -28644,12 +27993,8 @@
       <c r="O153" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P153" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A154" s="9" t="s">
         <v>435</v>
       </c>
@@ -28691,12 +28036,8 @@
       <c r="O154" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P154" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" s="9" t="s">
         <v>170</v>
       </c>
@@ -28742,12 +28083,8 @@
       <c r="O155" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P155" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" s="9" t="s">
         <v>226</v>
       </c>
@@ -28793,12 +28130,8 @@
       <c r="O156" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P156" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157" s="9" t="s">
         <v>324</v>
       </c>
@@ -28840,12 +28173,8 @@
       <c r="O157" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P157" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" s="9" t="s">
         <v>101</v>
       </c>
@@ -28887,12 +28216,8 @@
       <c r="O158" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P158" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159" s="9" t="s">
         <v>291</v>
       </c>
@@ -28938,12 +28263,8 @@
       <c r="O159" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P159" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160" s="9" t="s">
         <v>271</v>
       </c>
@@ -28989,12 +28310,8 @@
       <c r="O160" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P160" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A161" s="9" t="s">
         <v>386</v>
       </c>
@@ -29036,12 +28353,8 @@
       <c r="O161" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P161" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162" s="9" t="s">
         <v>466</v>
       </c>
@@ -29087,12 +28400,8 @@
       <c r="O162" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P162" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" s="9" t="s">
         <v>327</v>
       </c>
@@ -29134,12 +28443,8 @@
       <c r="O163" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P163" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" s="9" t="s">
         <v>215</v>
       </c>
@@ -29185,12 +28490,8 @@
       <c r="O164" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P164" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" s="9" t="s">
         <v>214</v>
       </c>
@@ -29236,12 +28537,8 @@
       <c r="O165" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P165" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A166" s="9" t="s">
         <v>221</v>
       </c>
@@ -29283,12 +28580,8 @@
       <c r="O166" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P166" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" s="9" t="s">
         <v>399</v>
       </c>
@@ -29334,12 +28627,8 @@
       <c r="O167" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P167" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A168" s="9" t="s">
         <v>188</v>
       </c>
@@ -29381,12 +28670,8 @@
       <c r="O168" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P168" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169" s="9" t="s">
         <v>119</v>
       </c>
@@ -29432,12 +28717,8 @@
       <c r="O169" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P169" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A170" s="9" t="s">
         <v>193</v>
       </c>
@@ -29483,12 +28764,8 @@
       <c r="O170" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P170" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A171" s="9" t="s">
         <v>44</v>
       </c>
@@ -29534,12 +28811,8 @@
       <c r="O171" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P171" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172" s="9" t="s">
         <v>88</v>
       </c>
@@ -29581,12 +28854,8 @@
       <c r="O172" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P172" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A173" s="9" t="s">
         <v>76</v>
       </c>
@@ -29632,12 +28901,8 @@
       <c r="O173" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P173" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A174" s="9" t="s">
         <v>376</v>
       </c>
@@ -29679,12 +28944,8 @@
       <c r="O174" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P174" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A175" s="9" t="s">
         <v>354</v>
       </c>
@@ -29730,12 +28991,8 @@
       <c r="O175" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P175" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A176" s="9" t="s">
         <v>343</v>
       </c>
@@ -29781,12 +29038,8 @@
       <c r="O176" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P176" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A177" s="9" t="s">
         <v>246</v>
       </c>
@@ -29832,12 +29085,8 @@
       <c r="O177" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P177" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A178" s="9" t="s">
         <v>351</v>
       </c>
@@ -29883,12 +29132,8 @@
       <c r="O178" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P178" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A179" s="9" t="s">
         <v>117</v>
       </c>
@@ -29930,12 +29175,8 @@
       <c r="O179" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P179" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A180" s="9" t="s">
         <v>429</v>
       </c>
@@ -29981,12 +29222,8 @@
       <c r="O180" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P180" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A181" s="9" t="s">
         <v>268</v>
       </c>
@@ -30032,12 +29269,8 @@
       <c r="O181" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P181" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A182" s="9" t="s">
         <v>444</v>
       </c>
@@ -30083,12 +29316,8 @@
       <c r="O182" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P182" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A183" s="9" t="s">
         <v>114</v>
       </c>
@@ -30134,12 +29363,8 @@
       <c r="O183" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P183" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A184" s="9" t="s">
         <v>265</v>
       </c>
@@ -30185,12 +29410,8 @@
       <c r="O184" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P184" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A185" s="9" t="s">
         <v>342</v>
       </c>
@@ -30236,12 +29457,8 @@
       <c r="O185" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P185" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A186" s="9" t="s">
         <v>261</v>
       </c>
@@ -30287,12 +29504,8 @@
       <c r="O186" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P186" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A187" s="9" t="s">
         <v>236</v>
       </c>
@@ -30338,12 +29551,8 @@
       <c r="O187" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P187" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A188" s="9" t="s">
         <v>121</v>
       </c>
@@ -30389,12 +29598,8 @@
       <c r="O188" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P188" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A189" s="9" t="s">
         <v>211</v>
       </c>
@@ -30436,12 +29641,8 @@
       <c r="O189" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P189" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A190" s="9" t="s">
         <v>148</v>
       </c>
@@ -30487,12 +29688,8 @@
       <c r="O190" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P190" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A191" s="9" t="s">
         <v>176</v>
       </c>
@@ -30534,12 +29731,8 @@
       <c r="O191" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P191" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A192" s="9" t="s">
         <v>337</v>
       </c>
@@ -30581,12 +29774,8 @@
       <c r="O192" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P192" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A193" s="9" t="s">
         <v>314</v>
       </c>
@@ -30632,12 +29821,8 @@
       <c r="O193" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P193" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A194" s="9" t="s">
         <v>306</v>
       </c>
@@ -30683,12 +29868,8 @@
       <c r="O194" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P194" s="10" t="str">
-        <f t="shared" ref="P194:P257" si="3">PROPER(TRIM(E194))</f>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A195" s="9" t="s">
         <v>202</v>
       </c>
@@ -30730,12 +29911,8 @@
       <c r="O195" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P195" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A196" s="9" t="s">
         <v>450</v>
       </c>
@@ -30777,12 +29954,8 @@
       <c r="O196" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P196" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A197" s="9" t="s">
         <v>74</v>
       </c>
@@ -30828,12 +30001,8 @@
       <c r="O197" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P197" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A198" s="9" t="s">
         <v>196</v>
       </c>
@@ -30879,12 +30048,8 @@
       <c r="O198" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P198" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A199" s="9" t="s">
         <v>96</v>
       </c>
@@ -30930,12 +30095,8 @@
       <c r="O199" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P199" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A200" s="9" t="s">
         <v>195</v>
       </c>
@@ -30981,12 +30142,8 @@
       <c r="O200" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P200" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A201" s="9" t="s">
         <v>452</v>
       </c>
@@ -31032,12 +30189,8 @@
       <c r="O201" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P201" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A202" s="9" t="s">
         <v>204</v>
       </c>
@@ -31083,12 +30236,8 @@
       <c r="O202" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P202" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A203" s="9" t="s">
         <v>433</v>
       </c>
@@ -31130,12 +30279,8 @@
       <c r="O203" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P203" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A204" s="9" t="s">
         <v>262</v>
       </c>
@@ -31181,12 +30326,8 @@
       <c r="O204" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P204" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A205" s="9" t="s">
         <v>344</v>
       </c>
@@ -31232,12 +30373,8 @@
       <c r="O205" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P205" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A206" s="9" t="s">
         <v>242</v>
       </c>
@@ -31283,12 +30420,8 @@
       <c r="O206" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P206" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A207" s="9" t="s">
         <v>156</v>
       </c>
@@ -31330,12 +30463,8 @@
       <c r="O207" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P207" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A208" s="9" t="s">
         <v>371</v>
       </c>
@@ -31381,12 +30510,8 @@
       <c r="O208" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P208" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A209" s="9" t="s">
         <v>455</v>
       </c>
@@ -31428,12 +30553,8 @@
       <c r="O209" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P209" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A210" s="9" t="s">
         <v>155</v>
       </c>
@@ -31479,12 +30600,8 @@
       <c r="O210" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P210" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A211" s="9" t="s">
         <v>379</v>
       </c>
@@ -31526,12 +30643,8 @@
       <c r="O211" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P211" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A212" s="9" t="s">
         <v>153</v>
       </c>
@@ -31577,12 +30690,8 @@
       <c r="O212" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P212" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A213" s="9" t="s">
         <v>349</v>
       </c>
@@ -31628,12 +30737,8 @@
       <c r="O213" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P213" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A214" s="9" t="s">
         <v>388</v>
       </c>
@@ -31675,12 +30780,8 @@
       <c r="O214" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P214" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A215" s="9" t="s">
         <v>240</v>
       </c>
@@ -31722,12 +30823,8 @@
       <c r="O215" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P215" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A216" s="9" t="s">
         <v>360</v>
       </c>
@@ -31769,12 +30866,8 @@
       <c r="O216" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P216" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A217" s="9" t="s">
         <v>158</v>
       </c>
@@ -31820,12 +30913,8 @@
       <c r="O217" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P217" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A218" s="9" t="s">
         <v>69</v>
       </c>
@@ -31871,12 +30960,8 @@
       <c r="O218" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P218" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A219" s="9" t="s">
         <v>85</v>
       </c>
@@ -31918,12 +31003,8 @@
       <c r="O219" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P219" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A220" s="9" t="s">
         <v>237</v>
       </c>
@@ -31969,12 +31050,8 @@
       <c r="O220" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P220" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A221" s="9" t="s">
         <v>430</v>
       </c>
@@ -32020,12 +31097,8 @@
       <c r="O221" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P221" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A222" s="9" t="s">
         <v>100</v>
       </c>
@@ -32067,12 +31140,8 @@
       <c r="O222" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P222" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A223" s="9" t="s">
         <v>243</v>
       </c>
@@ -32118,12 +31187,8 @@
       <c r="O223" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P223" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A224" s="9" t="s">
         <v>347</v>
       </c>
@@ -32169,12 +31234,8 @@
       <c r="O224" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P224" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A225" s="9" t="s">
         <v>136</v>
       </c>
@@ -32220,12 +31281,8 @@
       <c r="O225" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P225" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A226" s="9" t="s">
         <v>355</v>
       </c>
@@ -32271,12 +31328,8 @@
       <c r="O226" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P226" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A227" s="9" t="s">
         <v>178</v>
       </c>
@@ -32322,12 +31375,8 @@
       <c r="O227" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P227" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A228" s="9" t="s">
         <v>397</v>
       </c>
@@ -32373,12 +31422,8 @@
       <c r="O228" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P228" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A229" s="9" t="s">
         <v>299</v>
       </c>
@@ -32424,12 +31469,8 @@
       <c r="O229" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P229" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A230" s="9" t="s">
         <v>282</v>
       </c>
@@ -32475,12 +31516,8 @@
       <c r="O230" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P230" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A231" s="9" t="s">
         <v>126</v>
       </c>
@@ -32526,12 +31563,8 @@
       <c r="O231" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P231" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A232" s="9" t="s">
         <v>248</v>
       </c>
@@ -32577,12 +31610,8 @@
       <c r="O232" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P232" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A233" s="9" t="s">
         <v>416</v>
       </c>
@@ -32628,12 +31657,8 @@
       <c r="O233" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P233" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A234" s="9" t="s">
         <v>41</v>
       </c>
@@ -32679,12 +31704,8 @@
       <c r="O234" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P234" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A235" s="9" t="s">
         <v>367</v>
       </c>
@@ -32730,12 +31751,8 @@
       <c r="O235" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P235" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A236" s="9" t="s">
         <v>259</v>
       </c>
@@ -32777,12 +31794,8 @@
       <c r="O236" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P236" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A237" s="9" t="s">
         <v>353</v>
       </c>
@@ -32824,12 +31837,8 @@
       <c r="O237" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P237" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A238" s="9" t="s">
         <v>328</v>
       </c>
@@ -32871,12 +31880,8 @@
       <c r="O238" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P238" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A239" s="9" t="s">
         <v>222</v>
       </c>
@@ -32922,12 +31927,8 @@
       <c r="O239" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P239" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A240" s="9" t="s">
         <v>179</v>
       </c>
@@ -32969,12 +31970,8 @@
       <c r="O240" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P240" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A241" s="9" t="s">
         <v>310</v>
       </c>
@@ -33020,12 +32017,8 @@
       <c r="O241" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P241" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A242" s="9" t="s">
         <v>104</v>
       </c>
@@ -33071,12 +32064,8 @@
       <c r="O242" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P242" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A243" s="9" t="s">
         <v>301</v>
       </c>
@@ -33122,12 +32111,8 @@
       <c r="O243" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P243" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A244" s="9" t="s">
         <v>82</v>
       </c>
@@ -33173,12 +32158,8 @@
       <c r="O244" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P244" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A245" s="9" t="s">
         <v>319</v>
       </c>
@@ -33224,12 +32205,8 @@
       <c r="O245" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P245" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A246" s="9" t="s">
         <v>311</v>
       </c>
@@ -33275,12 +32252,8 @@
       <c r="O246" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P246" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A247" s="9" t="s">
         <v>72</v>
       </c>
@@ -33326,12 +32299,8 @@
       <c r="O247" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P247" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A248" s="9" t="s">
         <v>368</v>
       </c>
@@ -33377,12 +32346,8 @@
       <c r="O248" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P248" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A249" s="9" t="s">
         <v>219</v>
       </c>
@@ -33424,12 +32389,8 @@
       <c r="O249" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P249" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A250" s="9" t="s">
         <v>387</v>
       </c>
@@ -33475,12 +32436,8 @@
       <c r="O250" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P250" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A251" s="9" t="s">
         <v>56</v>
       </c>
@@ -33526,12 +32483,8 @@
       <c r="O251" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P251" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A252" s="9" t="s">
         <v>128</v>
       </c>
@@ -33577,12 +32530,8 @@
       <c r="O252" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P252" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A253" s="9" t="s">
         <v>263</v>
       </c>
@@ -33628,12 +32577,8 @@
       <c r="O253" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P253" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A254" s="9" t="s">
         <v>131</v>
       </c>
@@ -33675,12 +32620,8 @@
       <c r="O254" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P254" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A255" s="9" t="s">
         <v>191</v>
       </c>
@@ -33722,12 +32663,8 @@
       <c r="O255" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P255" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A256" s="9" t="s">
         <v>325</v>
       </c>
@@ -33773,12 +32710,8 @@
       <c r="O256" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P256" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A257" s="9" t="s">
         <v>110</v>
       </c>
@@ -33824,12 +32757,8 @@
       <c r="O257" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P257" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A258" s="9" t="s">
         <v>336</v>
       </c>
@@ -33875,12 +32804,8 @@
       <c r="O258" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P258" s="10" t="str">
-        <f t="shared" ref="P258:P321" si="4">PROPER(TRIM(E258))</f>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A259" s="9" t="s">
         <v>87</v>
       </c>
@@ -33926,12 +32851,8 @@
       <c r="O259" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P259" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A260" s="9" t="s">
         <v>124</v>
       </c>
@@ -33973,12 +32894,8 @@
       <c r="O260" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P260" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="261" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A261" s="9" t="s">
         <v>302</v>
       </c>
@@ -34024,12 +32941,8 @@
       <c r="O261" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P261" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="262" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A262" s="9" t="s">
         <v>390</v>
       </c>
@@ -34075,12 +32988,8 @@
       <c r="O262" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P262" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A263" s="9" t="s">
         <v>123</v>
       </c>
@@ -34126,12 +33035,8 @@
       <c r="O263" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P263" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A264" s="9" t="s">
         <v>174</v>
       </c>
@@ -34177,12 +33082,8 @@
       <c r="O264" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P264" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="265" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A265" s="9" t="s">
         <v>437</v>
       </c>
@@ -34224,12 +33125,8 @@
       <c r="O265" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P265" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="266" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A266" s="9" t="s">
         <v>462</v>
       </c>
@@ -34271,12 +33168,8 @@
       <c r="O266" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P266" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A267" s="9" t="s">
         <v>300</v>
       </c>
@@ -34318,12 +33211,8 @@
       <c r="O267" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P267" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A268" s="9" t="s">
         <v>238</v>
       </c>
@@ -34369,12 +33258,8 @@
       <c r="O268" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P268" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A269" s="9" t="s">
         <v>197</v>
       </c>
@@ -34416,12 +33301,8 @@
       <c r="O269" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P269" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="270" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A270" s="9" t="s">
         <v>307</v>
       </c>
@@ -34467,12 +33348,8 @@
       <c r="O270" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P270" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="271" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A271" s="9" t="s">
         <v>303</v>
       </c>
@@ -34518,12 +33395,8 @@
       <c r="O271" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P271" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="272" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A272" s="9" t="s">
         <v>171</v>
       </c>
@@ -34569,12 +33442,8 @@
       <c r="O272" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P272" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="273" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A273" s="9" t="s">
         <v>45</v>
       </c>
@@ -34620,12 +33489,8 @@
       <c r="O273" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P273" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="274" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A274" s="9" t="s">
         <v>112</v>
       </c>
@@ -34671,12 +33536,8 @@
       <c r="O274" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P274" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="275" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A275" s="9" t="s">
         <v>449</v>
       </c>
@@ -34722,12 +33583,8 @@
       <c r="O275" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P275" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="276" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A276" s="9" t="s">
         <v>220</v>
       </c>
@@ -34773,12 +33630,8 @@
       <c r="O276" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P276" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="277" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A277" s="9" t="s">
         <v>257</v>
       </c>
@@ -34824,12 +33677,8 @@
       <c r="O277" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P277" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="278" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A278" s="9" t="s">
         <v>249</v>
       </c>
@@ -34875,12 +33724,8 @@
       <c r="O278" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P278" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="279" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A279" s="9" t="s">
         <v>384</v>
       </c>
@@ -34926,12 +33771,8 @@
       <c r="O279" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P279" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="280" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A280" s="9" t="s">
         <v>62</v>
       </c>
@@ -34973,12 +33814,8 @@
       <c r="O280" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P280" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="281" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A281" s="9" t="s">
         <v>73</v>
       </c>
@@ -35024,12 +33861,8 @@
       <c r="O281" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P281" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="282" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A282" s="9" t="s">
         <v>160</v>
       </c>
@@ -35071,12 +33904,8 @@
       <c r="O282" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P282" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="283" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A283" s="9" t="s">
         <v>258</v>
       </c>
@@ -35122,12 +33951,8 @@
       <c r="O283" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P283" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="284" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A284" s="9" t="s">
         <v>331</v>
       </c>
@@ -35173,12 +33998,8 @@
       <c r="O284" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P284" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="285" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A285" s="9" t="s">
         <v>260</v>
       </c>
@@ -35224,12 +34045,8 @@
       <c r="O285" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P285" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="286" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A286" s="9" t="s">
         <v>233</v>
       </c>
@@ -35275,12 +34092,8 @@
       <c r="O286" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P286" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="287" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A287" s="9" t="s">
         <v>442</v>
       </c>
@@ -35322,12 +34135,8 @@
       <c r="O287" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P287" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="288" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A288" s="9" t="s">
         <v>118</v>
       </c>
@@ -35369,12 +34178,8 @@
       <c r="O288" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P288" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="289" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A289" s="9" t="s">
         <v>297</v>
       </c>
@@ -35416,12 +34221,8 @@
       <c r="O289" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P289" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="290" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A290" s="9" t="s">
         <v>279</v>
       </c>
@@ -35467,12 +34268,8 @@
       <c r="O290" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P290" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="291" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A291" s="9" t="s">
         <v>254</v>
       </c>
@@ -35518,12 +34315,8 @@
       <c r="O291" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P291" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="292" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A292" s="9" t="s">
         <v>396</v>
       </c>
@@ -35565,12 +34358,8 @@
       <c r="O292" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P292" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="293" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A293" s="9" t="s">
         <v>157</v>
       </c>
@@ -35616,12 +34405,8 @@
       <c r="O293" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P293" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="294" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A294" s="9" t="s">
         <v>448</v>
       </c>
@@ -35667,12 +34452,8 @@
       <c r="O294" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P294" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="295" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A295" s="9" t="s">
         <v>192</v>
       </c>
@@ -35718,12 +34499,8 @@
       <c r="O295" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P295" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="296" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A296" s="9" t="s">
         <v>280</v>
       </c>
@@ -35769,12 +34546,8 @@
       <c r="O296" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P296" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="297" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A297" s="9" t="s">
         <v>276</v>
       </c>
@@ -35816,12 +34589,8 @@
       <c r="O297" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P297" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="298" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A298" s="9" t="s">
         <v>412</v>
       </c>
@@ -35867,12 +34636,8 @@
       <c r="O298" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P298" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="299" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A299" s="9" t="s">
         <v>232</v>
       </c>
@@ -35918,12 +34683,8 @@
       <c r="O299" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P299" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="300" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A300" s="9" t="s">
         <v>167</v>
       </c>
@@ -35969,12 +34730,8 @@
       <c r="O300" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P300" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="301" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A301" s="9" t="s">
         <v>42</v>
       </c>
@@ -36016,12 +34773,8 @@
       <c r="O301" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P301" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="302" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A302" s="9" t="s">
         <v>201</v>
       </c>
@@ -36063,12 +34816,8 @@
       <c r="O302" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P302" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="303" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A303" s="9" t="s">
         <v>402</v>
       </c>
@@ -36114,12 +34863,8 @@
       <c r="O303" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P303" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="304" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="304" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A304" s="9" t="s">
         <v>28</v>
       </c>
@@ -36161,12 +34906,8 @@
       <c r="O304" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P304" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="305" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A305" s="9" t="s">
         <v>428</v>
       </c>
@@ -36212,12 +34953,8 @@
       <c r="O305" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P305" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="306" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A306" s="9" t="s">
         <v>281</v>
       </c>
@@ -36263,12 +35000,8 @@
       <c r="O306" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P306" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="307" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A307" s="9" t="s">
         <v>107</v>
       </c>
@@ -36314,12 +35047,8 @@
       <c r="O307" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P307" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="308" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="308" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A308" s="9" t="s">
         <v>177</v>
       </c>
@@ -36365,12 +35094,8 @@
       <c r="O308" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P308" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="309" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A309" s="9" t="s">
         <v>289</v>
       </c>
@@ -36412,12 +35137,8 @@
       <c r="O309" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P309" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="310" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="310" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A310" s="9" t="s">
         <v>183</v>
       </c>
@@ -36463,12 +35184,8 @@
       <c r="O310" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P310" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="311" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A311" s="9" t="s">
         <v>90</v>
       </c>
@@ -36510,12 +35227,8 @@
       <c r="O311" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P311" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="312" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A312" s="9" t="s">
         <v>329</v>
       </c>
@@ -36561,12 +35274,8 @@
       <c r="O312" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P312" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="313" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A313" s="9" t="s">
         <v>333</v>
       </c>
@@ -36608,12 +35317,8 @@
       <c r="O313" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P313" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="314" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A314" s="9" t="s">
         <v>95</v>
       </c>
@@ -36659,12 +35364,8 @@
       <c r="O314" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P314" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="315" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="315" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A315" s="9" t="s">
         <v>165</v>
       </c>
@@ -36710,12 +35411,8 @@
       <c r="O315" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P315" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="316" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="316" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A316" s="9" t="s">
         <v>151</v>
       </c>
@@ -36757,12 +35454,8 @@
       <c r="O316" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P316" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="317" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A317" s="9" t="s">
         <v>322</v>
       </c>
@@ -36804,12 +35497,8 @@
       <c r="O317" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P317" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="318" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="318" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A318" s="9" t="s">
         <v>357</v>
       </c>
@@ -36855,12 +35544,8 @@
       <c r="O318" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P318" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="319" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="319" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A319" s="9" t="s">
         <v>356</v>
       </c>
@@ -36906,12 +35591,8 @@
       <c r="O319" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P319" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="320" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A320" s="9" t="s">
         <v>443</v>
       </c>
@@ -36957,12 +35638,8 @@
       <c r="O320" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P320" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="321" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="321" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A321" s="9" t="s">
         <v>373</v>
       </c>
@@ -37004,12 +35681,8 @@
       <c r="O321" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P321" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="322" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="322" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A322" s="9" t="s">
         <v>187</v>
       </c>
@@ -37051,12 +35724,8 @@
       <c r="O322" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P322" s="10" t="str">
-        <f t="shared" ref="P322:P385" si="5">PROPER(TRIM(E322))</f>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="323" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="323" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A323" s="9" t="s">
         <v>92</v>
       </c>
@@ -37102,12 +35771,8 @@
       <c r="O323" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P323" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="324" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="324" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A324" s="9" t="s">
         <v>308</v>
       </c>
@@ -37153,12 +35818,8 @@
       <c r="O324" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P324" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="325" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="325" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A325" s="9" t="s">
         <v>434</v>
       </c>
@@ -37204,12 +35865,8 @@
       <c r="O325" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P325" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="326" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="326" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A326" s="9" t="s">
         <v>459</v>
       </c>
@@ -37255,12 +35912,8 @@
       <c r="O326" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P326" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="327" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A327" s="9" t="s">
         <v>144</v>
       </c>
@@ -37306,12 +35959,8 @@
       <c r="O327" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P327" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="328" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="328" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A328" s="9" t="s">
         <v>146</v>
       </c>
@@ -37357,12 +36006,8 @@
       <c r="O328" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P328" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="329" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="329" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A329" s="9" t="s">
         <v>53</v>
       </c>
@@ -37408,12 +36053,8 @@
       <c r="O329" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P329" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="330" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A330" s="9" t="s">
         <v>105</v>
       </c>
@@ -37459,12 +36100,8 @@
       <c r="O330" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P330" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="331" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="331" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A331" s="9" t="s">
         <v>287</v>
       </c>
@@ -37506,12 +36143,8 @@
       <c r="O331" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P331" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="332" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="332" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A332" s="9" t="s">
         <v>285</v>
       </c>
@@ -37557,12 +36190,8 @@
       <c r="O332" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P332" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="333" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="333" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A333" s="9" t="s">
         <v>207</v>
       </c>
@@ -37608,12 +36237,8 @@
       <c r="O333" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P333" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="334" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A334" s="9" t="s">
         <v>180</v>
       </c>
@@ -37659,12 +36284,8 @@
       <c r="O334" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P334" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="335" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="335" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A335" s="9" t="s">
         <v>403</v>
       </c>
@@ -37710,12 +36331,8 @@
       <c r="O335" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P335" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="336" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="336" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A336" s="9" t="s">
         <v>244</v>
       </c>
@@ -37761,12 +36378,8 @@
       <c r="O336" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P336" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="337" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="337" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A337" s="9" t="s">
         <v>398</v>
       </c>
@@ -37812,12 +36425,8 @@
       <c r="O337" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P337" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="338" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="338" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A338" s="9" t="s">
         <v>451</v>
       </c>
@@ -37859,12 +36468,8 @@
       <c r="O338" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P338" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="339" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="339" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A339" s="9" t="s">
         <v>185</v>
       </c>
@@ -37910,12 +36515,8 @@
       <c r="O339" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P339" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="340" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="340" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A340" s="9" t="s">
         <v>137</v>
       </c>
@@ -37961,12 +36562,8 @@
       <c r="O340" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P340" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="341" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="341" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A341" s="9" t="s">
         <v>447</v>
       </c>
@@ -38012,12 +36609,8 @@
       <c r="O341" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P341" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="342" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="342" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A342" s="9" t="s">
         <v>316</v>
       </c>
@@ -38063,12 +36656,8 @@
       <c r="O342" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P342" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="343" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="343" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A343" s="9" t="s">
         <v>169</v>
       </c>
@@ -38114,12 +36703,8 @@
       <c r="O343" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P343" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="344" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="344" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A344" s="9" t="s">
         <v>309</v>
       </c>
@@ -38165,12 +36750,8 @@
       <c r="O344" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P344" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="345" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="345" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A345" s="9" t="s">
         <v>274</v>
       </c>
@@ -38212,12 +36793,8 @@
       <c r="O345" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P345" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="346" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="346" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A346" s="9" t="s">
         <v>432</v>
       </c>
@@ -38263,12 +36840,8 @@
       <c r="O346" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P346" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="347" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="347" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A347" s="9" t="s">
         <v>152</v>
       </c>
@@ -38310,12 +36883,8 @@
       <c r="O347" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P347" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="348" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="348" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A348" s="9" t="s">
         <v>463</v>
       </c>
@@ -38361,12 +36930,8 @@
       <c r="O348" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P348" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="349" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="349" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A349" s="9" t="s">
         <v>441</v>
       </c>
@@ -38408,12 +36973,8 @@
       <c r="O349" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P349" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="350" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="350" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A350" s="9" t="s">
         <v>127</v>
       </c>
@@ -38455,12 +37016,8 @@
       <c r="O350" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P350" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="351" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="351" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A351" s="9" t="s">
         <v>122</v>
       </c>
@@ -38502,12 +37059,8 @@
       <c r="O351" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P351" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="352" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="352" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A352" s="9" t="s">
         <v>278</v>
       </c>
@@ -38553,12 +37106,8 @@
       <c r="O352" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P352" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="353" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="353" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A353" s="9" t="s">
         <v>60</v>
       </c>
@@ -38604,12 +37153,8 @@
       <c r="O353" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P353" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="354" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="354" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A354" s="9" t="s">
         <v>173</v>
       </c>
@@ -38651,12 +37196,8 @@
       <c r="O354" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P354" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="355" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="355" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A355" s="9" t="s">
         <v>227</v>
       </c>
@@ -38698,12 +37239,8 @@
       <c r="O355" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P355" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="356" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="356" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A356" s="9" t="s">
         <v>456</v>
       </c>
@@ -38749,12 +37286,8 @@
       <c r="O356" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P356" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="357" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="357" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A357" s="9" t="s">
         <v>464</v>
       </c>
@@ -38800,12 +37333,8 @@
       <c r="O357" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P357" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="358" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="358" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A358" s="9" t="s">
         <v>113</v>
       </c>
@@ -38851,12 +37380,8 @@
       <c r="O358" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P358" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="359" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="359" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A359" s="9" t="s">
         <v>424</v>
       </c>
@@ -38902,12 +37427,8 @@
       <c r="O359" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P359" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="360" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="360" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A360" s="9" t="s">
         <v>78</v>
       </c>
@@ -38949,12 +37470,8 @@
       <c r="O360" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P360" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="361" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="361" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A361" s="9" t="s">
         <v>365</v>
       </c>
@@ -38996,12 +37513,8 @@
       <c r="O361" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P361" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="362" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="362" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A362" s="9" t="s">
         <v>411</v>
       </c>
@@ -39047,12 +37560,8 @@
       <c r="O362" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P362" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="363" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="363" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A363" s="9" t="s">
         <v>425</v>
       </c>
@@ -39098,12 +37607,8 @@
       <c r="O363" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P363" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="364" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="364" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A364" s="9" t="s">
         <v>140</v>
       </c>
@@ -39149,12 +37654,8 @@
       <c r="O364" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P364" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="365" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="365" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A365" s="9" t="s">
         <v>426</v>
       </c>
@@ -39200,12 +37701,8 @@
       <c r="O365" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P365" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="366" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A366" s="9" t="s">
         <v>94</v>
       </c>
@@ -39251,12 +37748,8 @@
       <c r="O366" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P366" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="367" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="367" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A367" s="9" t="s">
         <v>275</v>
       </c>
@@ -39302,12 +37795,8 @@
       <c r="O367" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P367" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="368" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A368" s="9" t="s">
         <v>253</v>
       </c>
@@ -39353,12 +37842,8 @@
       <c r="O368" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P368" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="369" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A369" s="9" t="s">
         <v>184</v>
       </c>
@@ -39404,12 +37889,8 @@
       <c r="O369" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P369" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="370" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="370" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A370" s="9" t="s">
         <v>43</v>
       </c>
@@ -39451,12 +37932,8 @@
       <c r="O370" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P370" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="371" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="371" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A371" s="9" t="s">
         <v>375</v>
       </c>
@@ -39498,12 +37975,8 @@
       <c r="O371" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P371" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="372" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="372" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A372" s="9" t="s">
         <v>194</v>
       </c>
@@ -39549,12 +38022,8 @@
       <c r="O372" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P372" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="373" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="373" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A373" s="9" t="s">
         <v>323</v>
       </c>
@@ -39600,12 +38069,8 @@
       <c r="O373" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P373" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="374" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="374" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A374" s="9" t="s">
         <v>217</v>
       </c>
@@ -39651,12 +38116,8 @@
       <c r="O374" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P374" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="375" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="375" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A375" s="9" t="s">
         <v>209</v>
       </c>
@@ -39698,12 +38159,8 @@
       <c r="O375" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P375" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="376" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="376" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A376" s="9" t="s">
         <v>420</v>
       </c>
@@ -39745,12 +38202,8 @@
       <c r="O376" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P376" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="377" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="377" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A377" s="9" t="s">
         <v>83</v>
       </c>
@@ -39796,12 +38249,8 @@
       <c r="O377" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P377" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="378" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="378" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A378" s="9" t="s">
         <v>359</v>
       </c>
@@ -39847,12 +38296,8 @@
       <c r="O378" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P378" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="379" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A379" s="9" t="s">
         <v>364</v>
       </c>
@@ -39898,12 +38343,8 @@
       <c r="O379" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P379" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="380" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="380" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A380" s="9" t="s">
         <v>210</v>
       </c>
@@ -39949,12 +38390,8 @@
       <c r="O380" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P380" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="381" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A381" s="9" t="s">
         <v>154</v>
       </c>
@@ -40000,12 +38437,8 @@
       <c r="O381" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P381" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="382" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="382" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A382" s="9" t="s">
         <v>15</v>
       </c>
@@ -40047,12 +38480,8 @@
       <c r="O382" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P382" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="383" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="383" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A383" s="9" t="s">
         <v>439</v>
       </c>
@@ -40094,12 +38523,8 @@
       <c r="O383" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P383" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="384" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="384" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A384" s="9" t="s">
         <v>446</v>
       </c>
@@ -40145,12 +38570,8 @@
       <c r="O384" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P384" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="385" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="385" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A385" s="9" t="s">
         <v>149</v>
       </c>
@@ -40196,12 +38617,8 @@
       <c r="O385" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P385" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="386" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="386" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A386" s="9" t="s">
         <v>48</v>
       </c>
@@ -40247,12 +38664,8 @@
       <c r="O386" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P386" s="10" t="str">
-        <f t="shared" ref="P386:P421" si="6">PROPER(TRIM(E386))</f>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="387" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="387" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A387" s="9" t="s">
         <v>98</v>
       </c>
@@ -40298,12 +38711,8 @@
       <c r="O387" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P387" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="388" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="388" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A388" s="9" t="s">
         <v>66</v>
       </c>
@@ -40349,12 +38758,8 @@
       <c r="O388" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P388" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="389" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="389" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A389" s="9" t="s">
         <v>406</v>
       </c>
@@ -40400,12 +38805,8 @@
       <c r="O389" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P389" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="390" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="390" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A390" s="9" t="s">
         <v>422</v>
       </c>
@@ -40451,12 +38852,8 @@
       <c r="O390" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P390" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="391" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="391" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A391" s="9" t="s">
         <v>111</v>
       </c>
@@ -40502,12 +38899,8 @@
       <c r="O391" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P391" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="392" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="392" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A392" s="9" t="s">
         <v>363</v>
       </c>
@@ -40553,12 +38946,8 @@
       <c r="O392" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P392" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="393" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="393" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A393" s="9" t="s">
         <v>129</v>
       </c>
@@ -40600,12 +38989,8 @@
       <c r="O393" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P393" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="394" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="394" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A394" s="9" t="s">
         <v>205</v>
       </c>
@@ -40651,12 +39036,8 @@
       <c r="O394" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P394" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="395" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="395" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A395" s="9" t="s">
         <v>304</v>
       </c>
@@ -40702,12 +39083,8 @@
       <c r="O395" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P395" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="396" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="396" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A396" s="9" t="s">
         <v>352</v>
       </c>
@@ -40753,12 +39130,8 @@
       <c r="O396" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P396" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="397" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="397" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A397" s="9" t="s">
         <v>419</v>
       </c>
@@ -40804,12 +39177,8 @@
       <c r="O397" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P397" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="398" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="398" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A398" s="9" t="s">
         <v>58</v>
       </c>
@@ -40855,12 +39224,8 @@
       <c r="O398" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P398" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="399" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="399" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A399" s="9" t="s">
         <v>134</v>
       </c>
@@ -40906,12 +39271,8 @@
       <c r="O399" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P399" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="400" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="400" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A400" s="9" t="s">
         <v>166</v>
       </c>
@@ -40957,12 +39318,8 @@
       <c r="O400" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P400" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="401" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="401" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A401" s="9" t="s">
         <v>181</v>
       </c>
@@ -41004,12 +39361,8 @@
       <c r="O401" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P401" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="402" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="402" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A402" s="9" t="s">
         <v>467</v>
       </c>
@@ -41055,12 +39408,8 @@
       <c r="O402" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P402" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="403" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="403" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A403" s="9" t="s">
         <v>378</v>
       </c>
@@ -41106,12 +39455,8 @@
       <c r="O403" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P403" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="404" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="404" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A404" s="9" t="s">
         <v>186</v>
       </c>
@@ -41153,12 +39498,8 @@
       <c r="O404" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P404" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="405" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="405" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A405" s="9" t="s">
         <v>457</v>
       </c>
@@ -41200,12 +39541,8 @@
       <c r="O405" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P405" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="406" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="406" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A406" s="9" t="s">
         <v>266</v>
       </c>
@@ -41251,12 +39588,8 @@
       <c r="O406" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P406" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="407" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="407" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A407" s="9" t="s">
         <v>267</v>
       </c>
@@ -41302,12 +39635,8 @@
       <c r="O407" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P407" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="408" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="408" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A408" s="9" t="s">
         <v>225</v>
       </c>
@@ -41353,12 +39682,8 @@
       <c r="O408" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P408" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Beauty</v>
-      </c>
-    </row>
-    <row r="409" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="409" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A409" s="9" t="s">
         <v>109</v>
       </c>
@@ -41404,12 +39729,8 @@
       <c r="O409" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P409" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="410" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="410" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A410" s="9" t="s">
         <v>440</v>
       </c>
@@ -41455,12 +39776,8 @@
       <c r="O410" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P410" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="411" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="411" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A411" s="9" t="s">
         <v>34</v>
       </c>
@@ -41502,12 +39819,8 @@
       <c r="O411" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P411" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="412" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="412" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A412" s="9" t="s">
         <v>125</v>
       </c>
@@ -41553,12 +39866,8 @@
       <c r="O412" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P412" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Grocery</v>
-      </c>
-    </row>
-    <row r="413" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="413" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A413" s="9" t="s">
         <v>143</v>
       </c>
@@ -41604,12 +39913,8 @@
       <c r="O413" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P413" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="414" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="414" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A414" s="9" t="s">
         <v>162</v>
       </c>
@@ -41655,12 +39960,8 @@
       <c r="O414" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P414" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="415" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="415" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A415" s="9" t="s">
         <v>103</v>
       </c>
@@ -41706,12 +40007,8 @@
       <c r="O415" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P415" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="416" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="416" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A416" s="9" t="s">
         <v>37</v>
       </c>
@@ -41757,12 +40054,8 @@
       <c r="O416" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P416" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Home &amp; Living</v>
-      </c>
-    </row>
-    <row r="417" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="417" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A417" s="9" t="s">
         <v>335</v>
       </c>
@@ -41804,12 +40097,8 @@
       <c r="O417" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P417" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="418" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="418" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A418" s="9" t="s">
         <v>453</v>
       </c>
@@ -41855,12 +40144,8 @@
       <c r="O418" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P418" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Fashion</v>
-      </c>
-    </row>
-    <row r="419" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="419" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A419" s="9" t="s">
         <v>97</v>
       </c>
@@ -41906,12 +40191,8 @@
       <c r="O419" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P419" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="420" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="420" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A420" s="9" t="s">
         <v>172</v>
       </c>
@@ -41957,60 +40238,52 @@
       <c r="O420" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P420" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>Electronics</v>
-      </c>
-    </row>
-    <row r="421" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A421" s="11" t="s">
+    </row>
+    <row r="421" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A421" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="B421" s="12">
+      <c r="B421" s="11">
         <v>45842</v>
       </c>
-      <c r="C421" s="13" t="s">
+      <c r="C421" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D421" s="13" t="s">
+      <c r="D421" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E421" s="13" t="s">
+      <c r="E421" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F421" s="13" t="s">
+      <c r="F421" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G421" s="13">
+      <c r="G421" s="12">
         <v>5</v>
       </c>
-      <c r="H421" s="13">
+      <c r="H421" s="12">
         <v>186.46</v>
       </c>
-      <c r="I421" s="13">
+      <c r="I421" s="12">
         <v>0.15</v>
       </c>
-      <c r="J421" s="13">
+      <c r="J421" s="12">
         <v>792.46</v>
       </c>
-      <c r="K421" s="13">
+      <c r="K421" s="12">
         <v>455.28</v>
       </c>
-      <c r="L421" s="13" t="s">
+      <c r="L421" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="M421" s="13">
+      <c r="M421" s="12">
         <v>3</v>
       </c>
-      <c r="N421" s="13">
+      <c r="N421" s="12">
         <v>1</v>
       </c>
-      <c r="O421" s="13" t="s">
+      <c r="O421" s="12" t="s">
         <v>27</v>
-      </c>
-      <c r="P421" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Electronics</v>
       </c>
     </row>
   </sheetData>
@@ -42037,142 +40310,142 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="34" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="22" t="s">
         <v>508</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="E2" s="23"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
+      <c r="B3" s="22" t="s">
         <v>509</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="C3" s="22" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
         <v>510</v>
       </c>
-      <c r="C3" s="25" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
-        <v>511</v>
-      </c>
-      <c r="B4" s="26">
+      <c r="B4" s="23">
         <f>COUNTA(Raw_Data!A2:A421)</f>
         <v>420</v>
       </c>
-      <c r="C4" s="26" t="s">
-        <v>524</v>
+      <c r="C4" s="23" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
-        <v>512</v>
-      </c>
-      <c r="B5" s="26">
+      <c r="A5" s="23" t="s">
+        <v>511</v>
+      </c>
+      <c r="B5" s="23">
         <f>COUNTBLANK(Raw_Data!J2:J421)</f>
         <v>0</v>
       </c>
-      <c r="C5" s="26" t="s">
-        <v>524</v>
+      <c r="C5" s="23" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="26" t="s">
-        <v>515</v>
-      </c>
-      <c r="B6" s="27">
+      <c r="A6" s="23" t="s">
+        <v>514</v>
+      </c>
+      <c r="B6" s="24">
         <f>COUNTIF(Raw_Data!N2:N421,"&lt;1")+COUNTIF(Raw_Data!N2:N421,"&gt;5")</f>
         <v>1</v>
       </c>
-      <c r="C6" s="26" t="s">
-        <v>517</v>
+      <c r="C6" s="23" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="26" t="s">
-        <v>513</v>
-      </c>
-      <c r="B7" s="26">
+      <c r="A7" s="23" t="s">
+        <v>512</v>
+      </c>
+      <c r="B7" s="23">
         <f>COUNTIF(Raw_Data!G2:G421,"&lt;=0")</f>
         <v>1</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="23" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="23" t="s">
+        <v>513</v>
+      </c>
+      <c r="B8" s="23">
+        <v>0</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="23" t="s">
+        <v>515</v>
+      </c>
+      <c r="B9" s="23">
+        <v>1</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="115.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="23" t="s">
+        <v>519</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>520</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="150.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="23" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="26" t="s">
-        <v>514</v>
-      </c>
-      <c r="B8" s="26">
-        <v>0</v>
-      </c>
-      <c r="C8" s="26" t="s">
+      <c r="B11" s="24" t="s">
+        <v>518</v>
+      </c>
+      <c r="C11" s="23" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="26" t="s">
-        <v>516</v>
-      </c>
-      <c r="B9" s="26">
-        <v>1</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="115.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26" t="s">
-        <v>520</v>
-      </c>
-      <c r="B10" s="26" t="s">
+    <row r="12" spans="1:5" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="23" t="s">
         <v>521</v>
       </c>
-      <c r="C10" s="26" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="150.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26" t="s">
-        <v>518</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>519</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26" t="s">
-        <v>522</v>
-      </c>
-      <c r="B12" s="26">
+      <c r="B12" s="23">
         <f>COUNTBLANK(Raw_Data!N2:N421)</f>
         <v>112</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="23" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="181.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="23" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="181.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26" t="s">
-        <v>518</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>523</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>525</v>
+      <c r="B13" s="23" t="s">
+        <v>522</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -42273,91 +40546,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>484</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>485</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="21">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="18" t="s">
         <v>487</v>
       </c>
-      <c r="C2" s="22" t="s">
-        <v>507</v>
+      <c r="C2" s="19" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="21">
+      <c r="A3" s="18">
         <v>2</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="18" t="s">
         <v>488</v>
       </c>
-      <c r="C3" s="22" t="s">
-        <v>507</v>
+      <c r="C3" s="19" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="21">
+      <c r="A4" s="18">
         <v>3</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="18" t="s">
         <v>489</v>
       </c>
-      <c r="C4" s="22" t="s">
-        <v>507</v>
+      <c r="C4" s="19" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="21">
+      <c r="A5" s="18">
         <v>4</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="18" t="s">
         <v>490</v>
       </c>
-      <c r="C5" s="22" t="s">
-        <v>507</v>
+      <c r="C5" s="19" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="21">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="18" t="s">
         <v>491</v>
       </c>
-      <c r="C6" s="22" t="s">
-        <v>507</v>
+      <c r="C6" s="19" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="21">
+      <c r="A7" s="18">
         <v>6</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="18" t="s">
         <v>492</v>
       </c>
-      <c r="C7" s="22" t="s">
-        <v>507</v>
+      <c r="C7" s="19" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="21">
+      <c r="A8" s="18">
         <v>7</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="18" t="s">
         <v>493</v>
       </c>
-      <c r="C8" s="22" t="s">
-        <v>507</v>
+      <c r="C8" s="19" t="s">
+        <v>506</v>
       </c>
     </row>
   </sheetData>
